--- a/Assessment Questions/CDA/DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment/Keys_MySQL_Hybrid.xlsx
+++ b/Assessment Questions/CDA/DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment/Keys_MySQL_Hybrid.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,440 +413,658 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Module:</t>
+          <t>Question No.</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Keys (MySQL)</t>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Keys_MySQL_Hybrid</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Write an SQL query to list all records needed for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SELECT Basics</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Q.No</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Scenario-Based Question</t>
+          <t>Write an SQL query to filter records relevant to Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>WHERE Filtering</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Create a table with emp_id as PRIMARY KEY.</t>
+          <t>Write an SQL query that sorts the result for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ORDER BY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Create a table with composite primary key (emp_id, dept_id).</t>
+          <t>Write an SQL query that counts records related to Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>COUNT Aggregation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Create two tables with FOREIGN KEY relationship.</t>
+          <t>Write an SQL query that groups the result set for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GROUP BY</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Create a table with UNIQUE constraint as candidate key.</t>
+          <t>Write an SQL query that calculates an average or summary for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Aggregate Functions</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alter table to add PRIMARY KEY.</t>
+          <t>Write an SQL query to find the highest-value result in Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MAX / TOP Analysis</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Alter table to add FOREIGN KEY.</t>
+          <t>Write an SQL query to find the lowest-value result in Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MIN Analysis</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Design a table with composite key and explain usage.</t>
+          <t>Write an SQL query that joins two tables for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JOIN Logic</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Create a schema where multiple candidate keys exist.</t>
+          <t>Write an SQL query using aliases to improve readability for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Aliases</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Create table ensuring email is unique.</t>
+          <t>Write an SQL query that uses a subquery for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Subqueries</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Add FOREIGN KEY with ON DELETE CASCADE.</t>
+          <t>Write an SQL query that uses HAVING with grouped data for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HAVING Clause</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Design relational schema using multiple keys.</t>
+          <t>Write an SQL query to find duplicate records related to Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Duplicate Detection</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Create table with both PRIMARY KEY and UNIQUE constraints.</t>
+          <t>Write an SQL query that updates rows associated with Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UPDATE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>What is a primary key?</t>
+          <t>Write an SQL query that deletes rows based on a condition in Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Difference between candidate key and primary key.</t>
+          <t>Write an SQL query to create a view for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Views</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Explain super key with example.</t>
+          <t>Write an SQL query that uses CASE logic for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CASE Expressions</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>What is composite key?</t>
+          <t>Write an SQL query that ranks rows for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Window Functions</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Why cannot primary key be NULL?</t>
+          <t>Write an SQL query that returns only distinct values for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DISTINCT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Keys_MySQL_Hybrid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Difference between super key and candidate key.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Concept</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Explain foreign key with example.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Concept</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Explain role of keys in normalization.</t>
+          <t>Write an SQL query to validate data quality for Keys_MySQL_Hybrid.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Course CDA | DBM-120/Data Types and Constraints/Primary key, Foreign key, Not null, Unique, Check, default, Auto increment</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Data Quality Checks</t>
         </is>
       </c>
     </row>
